--- a/8DIO/Claire Woodwinds/Claire Piccolo Flute Virtuoso/xlsx/Claire Piccolo Flute Virtuoso.xlsx
+++ b/8DIO/Claire Woodwinds/Claire Piccolo Flute Virtuoso/xlsx/Claire Piccolo Flute Virtuoso.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="21555" windowHeight="10530" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="21555" windowHeight="10530"/>
   </bookViews>
   <sheets>
     <sheet name="Piccolo Arcs" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -53,6 +68,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -75,6 +105,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -103,6 +148,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -128,6 +188,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -144,7 +219,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="175">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -667,13 +742,31 @@
   </si>
   <si>
     <t>STRONG</t>
+  </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>Piccolo Arcs</t>
+  </si>
+  <si>
+    <t>Piccolo Bonus FX Runs</t>
+  </si>
+  <si>
+    <t>Piccolo Leg Lyrical</t>
+  </si>
+  <si>
+    <t>Piccolo Leg Strong</t>
+  </si>
+  <si>
+    <t>Piccolo General Arts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -720,8 +813,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -767,6 +867,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -824,7 +930,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -890,6 +996,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1192,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -1205,95 +1317,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>144</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>161</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -1301,25 +1374,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -1328,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -1339,13 +1408,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -1354,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -1365,13 +1434,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -1380,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -1390,14 +1459,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>165</v>
+      <c r="A8" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>165</v>
+      <c r="C8" s="17" t="s">
+        <v>163</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -1406,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -1416,14 +1485,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>166</v>
+      <c r="A9" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>166</v>
+      <c r="C9" s="17" t="s">
+        <v>164</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -1432,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -1442,25 +1511,53 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="6">
+        <v>120</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
@@ -1468,7 +1565,7 @@
     <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="2"/>
@@ -1480,7 +1577,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -2869,17 +2966,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -2894,19 +3018,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2916,7 +3040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -2929,95 +3053,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>146</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -3025,25 +3110,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -3052,7 +3133,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -3063,13 +3144,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -3078,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -3089,13 +3170,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -3104,7 +3185,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -3114,14 +3195,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>150</v>
+      <c r="A8" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>150</v>
+      <c r="C8" s="17" t="s">
+        <v>148</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -3130,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -3140,25 +3221,53 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6">
+        <v>120</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="6">
+        <v>120</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="3"/>
@@ -3178,7 +3287,7 @@
     <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="2"/>
@@ -3190,7 +3299,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -4579,18 +4688,45 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4604,19 +4740,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="Choose from Drop-down list" prompt="If don’t use MIDI Note, set Cell value empty">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4626,7 +4762,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -4639,95 +4775,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -4735,25 +4832,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -4762,7 +4855,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -4773,13 +4866,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -4788,7 +4881,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -4799,13 +4892,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -4814,7 +4907,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -4824,14 +4917,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>159</v>
+      <c r="A8" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>159</v>
+      <c r="C8" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -4840,7 +4933,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -4850,14 +4943,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>151</v>
+      <c r="A9" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>151</v>
+      <c r="C9" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -4866,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -4877,13 +4970,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -4892,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -4902,25 +4995,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -4928,7 +5049,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -6317,18 +6438,45 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6342,19 +6490,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="Choose from Drop-down list" prompt="If don’t use MIDI Note, set Cell value empty">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6364,7 +6512,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -6377,95 +6525,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>173</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>167</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -6473,25 +6582,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -6500,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -6511,13 +6616,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -6526,7 +6631,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -6537,13 +6642,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -6552,7 +6657,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -6562,14 +6667,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>159</v>
+      <c r="A8" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>159</v>
+      <c r="C8" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -6578,7 +6683,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -6588,14 +6693,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>151</v>
+      <c r="A9" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>151</v>
+      <c r="C9" s="17" t="s">
+        <v>168</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -6604,7 +6709,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -6615,13 +6720,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -6630,7 +6735,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -6640,25 +6745,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -6666,7 +6799,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -8055,17 +8188,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -8080,19 +8240,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8102,7 +8262,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -8115,95 +8275,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>152</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -8211,25 +8332,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -8238,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -8249,13 +8366,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -8264,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -8275,13 +8392,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -8290,7 +8407,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -8300,14 +8417,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>155</v>
+      <c r="A8" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>155</v>
+      <c r="C8" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -8316,7 +8433,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -8326,25 +8443,53 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6">
+        <v>120</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="6">
+        <v>120</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="3"/>
@@ -8364,7 +8509,7 @@
     <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="2"/>
@@ -8376,7 +8521,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -9765,17 +9910,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -9790,19 +9962,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
